--- a/data/trans_orig/P37-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P37-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2007</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50172</t>
+          <t>48749</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81192</t>
+          <t>80390</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26909</t>
+          <t>27831</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49454</t>
+          <t>50897</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83557</t>
+          <t>83825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120207</t>
+          <t>120575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>392584</t>
+          <t>393386</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>423604</t>
+          <t>425027</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>257226</t>
+          <t>255783</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279771</t>
+          <t>278849</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>660250</t>
+          <t>659882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>696900</t>
+          <t>696632</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,26%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45499</t>
+          <t>45241</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74953</t>
+          <t>73534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17512</t>
+          <t>17143</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38098</t>
+          <t>36967</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68951</t>
+          <t>68679</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102195</t>
+          <t>102810</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>291981</t>
+          <t>293400</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>321435</t>
+          <t>321693</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>332786</t>
+          <t>333917</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>353372</t>
+          <t>353741</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>635623</t>
+          <t>635008</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>668867</t>
+          <t>669139</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53233</t>
+          <t>53496</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82979</t>
+          <t>83106</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13810</t>
+          <t>14136</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31240</t>
+          <t>31206</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72545</t>
+          <t>73368</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107335</t>
+          <t>108157</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>459410</t>
+          <t>459283</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>489156</t>
+          <t>488893</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136542</t>
+          <t>136576</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153972</t>
+          <t>153646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602836</t>
+          <t>602014</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>637626</t>
+          <t>636803</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,67%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>180794</t>
+          <t>179743</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>232023</t>
+          <t>230559</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76080</t>
+          <t>75621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111088</t>
+          <t>111944</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>267968</t>
+          <t>265418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>333400</t>
+          <t>325594</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1006311</t>
+          <t>1007775</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1057540</t>
+          <t>1058591</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>603197</t>
+          <t>602341</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>638205</t>
+          <t>638664</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1619220</t>
+          <t>1627026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1684652</t>
+          <t>1687202</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,41%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36259</t>
+          <t>38433</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64593</t>
+          <t>64893</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63924</t>
+          <t>63475</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97776</t>
+          <t>99595</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>110801</t>
+          <t>110656</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154077</t>
+          <t>156324</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>285112</t>
+          <t>284812</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>313446</t>
+          <t>311272</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>470976</t>
+          <t>469157</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>504828</t>
+          <t>505277</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>764380</t>
+          <t>762133</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>807656</t>
+          <t>807801</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,95%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20177</t>
+          <t>20180</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>248759</t>
+          <t>247947</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>308031</t>
+          <t>305879</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>258131</t>
+          <t>259153</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>319479</t>
+          <t>319758</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>277109</t>
+          <t>277106</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290517</t>
+          <t>290690</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>939813</t>
+          <t>941965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>999085</t>
+          <t>999897</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1225651</t>
+          <t>1225372</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1286999</t>
+          <t>1285977</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,23%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>416200</t>
+          <t>417111</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>493455</t>
+          <t>493850</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>496126</t>
+          <t>496309</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>581322</t>
+          <t>575906</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>932910</t>
+          <t>933432</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1042821</t>
+          <t>1046199</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2774970</t>
+          <t>2774575</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2852225</t>
+          <t>2851314</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2794905</t>
+          <t>2800321</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2880101</t>
+          <t>2879918</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5601831</t>
+          <t>5598453</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5711742</t>
+          <t>5711220</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,95%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2012</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52396</t>
+          <t>51277</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84474</t>
+          <t>82999</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26091</t>
+          <t>25558</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49455</t>
+          <t>50685</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83344</t>
+          <t>83412</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125240</t>
+          <t>121951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>351722</t>
+          <t>353197</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383800</t>
+          <t>384919</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264999</t>
+          <t>263769</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288363</t>
+          <t>288896</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>625410</t>
+          <t>628699</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>667306</t>
+          <t>667238</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62227</t>
+          <t>64167</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99107</t>
+          <t>98965</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>21823</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46256</t>
+          <t>44812</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89777</t>
+          <t>90860</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>132047</t>
+          <t>133789</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>319690</t>
+          <t>319832</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>356570</t>
+          <t>354630</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>290684</t>
+          <t>292128</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>314878</t>
+          <t>315117</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>623690</t>
+          <t>621948</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>665960</t>
+          <t>664877</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92816</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134704</t>
+          <t>133508</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22709</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45073</t>
+          <t>42895</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122173</t>
+          <t>121465</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168040</t>
+          <t>169319</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>493681</t>
+          <t>494877</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535569</t>
+          <t>535261</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>215056</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>237420</t>
+          <t>238677</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>720475</t>
+          <t>719196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>766342</t>
+          <t>767050</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,33%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>202852</t>
+          <t>201305</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>256610</t>
+          <t>257694</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75336</t>
+          <t>75929</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111263</t>
+          <t>115640</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>290195</t>
+          <t>287949</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>354751</t>
+          <t>355920</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>902399</t>
+          <t>901315</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>956157</t>
+          <t>957704</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>655394</t>
+          <t>651017</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>691321</t>
+          <t>690728</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1570916</t>
+          <t>1569747</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1635472</t>
+          <t>1637718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,05%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77239</t>
+          <t>77341</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112538</t>
+          <t>111734</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>129664</t>
+          <t>128932</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>172610</t>
+          <t>173064</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>218011</t>
+          <t>218068</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>274640</t>
+          <t>272428</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>397031</t>
+          <t>397835</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>432330</t>
+          <t>432228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>588912</t>
+          <t>588458</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>631858</t>
+          <t>632590</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>996451</t>
+          <t>998663</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1053080</t>
+          <t>1053023</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14357</t>
+          <t>14292</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34394</t>
+          <t>33996</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>274370</t>
+          <t>275608</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>336230</t>
+          <t>337332</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>296345</t>
+          <t>292696</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>358440</t>
+          <t>356889</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,97%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230536</t>
+          <t>230934</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250573</t>
+          <t>250638</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>773121</t>
+          <t>772019</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>834981</t>
+          <t>833743</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1015841</t>
+          <t>1017392</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1077936</t>
+          <t>1081585</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,7%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>558810</t>
+          <t>560676</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>651477</t>
+          <t>646853</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>600523</t>
+          <t>600878</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>697359</t>
+          <t>696172</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1178917</t>
+          <t>1182665</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1315924</t>
+          <t>1315438</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2765409</t>
+          <t>2770033</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2858076</t>
+          <t>2856210</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2851695</t>
+          <t>2852882</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2948531</t>
+          <t>2948176</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5650016</t>
+          <t>5650502</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5787023</t>
+          <t>5783275</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,02%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2016</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49818</t>
+          <t>51039</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81700</t>
+          <t>81710</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33593</t>
+          <t>33318</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60356</t>
+          <t>62272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91926</t>
+          <t>91576</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132997</t>
+          <t>133082</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>347392</t>
+          <t>347382</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>379274</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286699</t>
+          <t>284783</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313462</t>
+          <t>313737</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>643150</t>
+          <t>643065</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>684221</t>
+          <t>684571</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,2%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38096</t>
+          <t>37952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64591</t>
+          <t>64659</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23254</t>
+          <t>22955</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46118</t>
+          <t>45608</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67510</t>
+          <t>67424</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104861</t>
+          <t>102478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>312636</t>
+          <t>312568</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>339131</t>
+          <t>339275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326155</t>
+          <t>326665</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349019</t>
+          <t>349318</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>644639</t>
+          <t>647022</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>681990</t>
+          <t>682076</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74377</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106989</t>
+          <t>108172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19270</t>
+          <t>19564</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40928</t>
+          <t>39665</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100020</t>
+          <t>100339</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140869</t>
+          <t>139288</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>414925</t>
+          <t>413742</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>447537</t>
+          <t>449629</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125195</t>
+          <t>126458</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>146853</t>
+          <t>146559</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>547167</t>
+          <t>548748</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>588016</t>
+          <t>587697</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172981</t>
+          <t>171870</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>223003</t>
+          <t>222817</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82999</t>
+          <t>84632</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120972</t>
+          <t>124049</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>267814</t>
+          <t>267315</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>331475</t>
+          <t>330557</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>926635</t>
+          <t>926821</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>976657</t>
+          <t>977768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>704904</t>
+          <t>701827</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>742877</t>
+          <t>741244</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1644039</t>
+          <t>1644957</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1707700</t>
+          <t>1708199</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,47%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95099</t>
+          <t>96911</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>134533</t>
+          <t>135082</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>103010</t>
+          <t>103083</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144645</t>
+          <t>145380</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>212135</t>
+          <t>210379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>267301</t>
+          <t>265194</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>486173</t>
+          <t>485624</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>525607</t>
+          <t>523795</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>593599</t>
+          <t>592864</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>635234</t>
+          <t>635161</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1091649</t>
+          <t>1093756</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1146815</t>
+          <t>1148571</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>10398</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27099</t>
+          <t>27109</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>243337</t>
+          <t>243726</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>303640</t>
+          <t>304513</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>257198</t>
+          <t>260345</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>322969</t>
+          <t>322355</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>260046</t>
+          <t>260036</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>277368</t>
+          <t>276747</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>778385</t>
+          <t>777512</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>838688</t>
+          <t>838299</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1046201</t>
+          <t>1046815</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1111972</t>
+          <t>1108825</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>80,99%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>491185</t>
+          <t>495989</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>573598</t>
+          <t>577202</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>558653</t>
+          <t>559667</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>653862</t>
+          <t>655704</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1076405</t>
+          <t>1077897</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1199428</t>
+          <t>1205914</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2812124</t>
+          <t>2808520</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2894537</t>
+          <t>2889733</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2877734</t>
+          <t>2875892</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2972943</t>
+          <t>2971929</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5717890</t>
+          <t>5711404</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5840913</t>
+          <t>5839421</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,42%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2023</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2023 (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>168547</t>
+          <t>170456</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>210397</t>
+          <t>215108</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>146112</t>
+          <t>146712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>179960</t>
+          <t>181851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>325916</t>
+          <t>328519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>382984</t>
+          <t>385345</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,45%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>294815</t>
+          <t>290104</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>336665</t>
+          <t>334756</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267507</t>
+          <t>265616</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>301355</t>
+          <t>300755</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>569695</t>
+          <t>567334</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>626763</t>
+          <t>624160</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,52%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148445</t>
+          <t>148493</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>187514</t>
+          <t>190195</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>102434</t>
+          <t>102128</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>132244</t>
+          <t>131812</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>258971</t>
+          <t>258785</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>308899</t>
+          <t>310145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>264699</t>
+          <t>262018</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>303768</t>
+          <t>303720</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>250336</t>
+          <t>250768</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>280146</t>
+          <t>280452</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>525894</t>
+          <t>524648</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>575822</t>
+          <t>576008</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,0%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50268</t>
+          <t>56111</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>222763</t>
+          <t>224603</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>56135</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76502</t>
+          <t>75731</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83444</t>
+          <t>90331</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>293728</t>
+          <t>292084</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>445501</t>
+          <t>443661</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>617996</t>
+          <t>612153</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90409</t>
+          <t>91180</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110358</t>
+          <t>110776</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>541447</t>
+          <t>543091</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>751731</t>
+          <t>744844</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,18%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>316102</t>
+          <t>314864</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>377880</t>
+          <t>378911</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>292837</t>
+          <t>293659</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>705024</t>
+          <t>654919</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>637141</t>
+          <t>637342</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1138797</t>
+          <t>1154243</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>57,34%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>656939</t>
+          <t>655908</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>718717</t>
+          <t>719955</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>273070</t>
+          <t>323175</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>685257</t>
+          <t>684435</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>874115</t>
+          <t>858669</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1375771</t>
+          <t>1375570</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,34%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110902</t>
+          <t>109552</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>148983</t>
+          <t>147834</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>198802</t>
+          <t>199457</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>304974</t>
+          <t>305586</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>320440</t>
+          <t>307689</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>434482</t>
+          <t>433357</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>326063</t>
+          <t>327212</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>364144</t>
+          <t>365494</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>534022</t>
+          <t>533410</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>640194</t>
+          <t>639539</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>879559</t>
+          <t>880684</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>993601</t>
+          <t>1006352</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,58%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6512</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26427</t>
+          <t>26946</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>323534</t>
+          <t>327708</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>375573</t>
+          <t>374763</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>333317</t>
+          <t>329664</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>394159</t>
+          <t>391740</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>214080</t>
+          <t>213561</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233840</t>
+          <t>233995</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>385798</t>
+          <t>386608</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>437837</t>
+          <t>433663</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>607719</t>
+          <t>610138</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>668561</t>
+          <t>672214</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,1%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>766921</t>
+          <t>781514</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1078157</t>
+          <t>1071862</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1243874</t>
+          <t>1252539</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1809090</t>
+          <t>1879841</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2153703</t>
+          <t>2149000</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2823420</t>
+          <t>2831238</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2297903</t>
+          <t>2304198</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2609139</t>
+          <t>2594546</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1766328</t>
+          <t>1695577</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2331544</t>
+          <t>2322879</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4128059</t>
+          <t>4120241</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4797776</t>
+          <t>4802479</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P37-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48749</t>
+          <t>49868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80390</t>
+          <t>80529</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27831</t>
+          <t>26869</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50897</t>
+          <t>49817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83825</t>
+          <t>84219</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120575</t>
+          <t>121575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>393386</t>
+          <t>393247</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425027</t>
+          <t>423908</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>255783</t>
+          <t>256863</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>278849</t>
+          <t>279811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>659882</t>
+          <t>658882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>696632</t>
+          <t>696238</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45241</t>
+          <t>45743</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73534</t>
+          <t>74984</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17143</t>
+          <t>17212</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36967</t>
+          <t>37872</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68679</t>
+          <t>68634</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102810</t>
+          <t>105368</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>293400</t>
+          <t>291950</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>321693</t>
+          <t>321191</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>333917</t>
+          <t>333012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>353741</t>
+          <t>353672</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>635008</t>
+          <t>632450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>669139</t>
+          <t>669184</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53496</t>
+          <t>54446</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83106</t>
+          <t>83524</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>12807</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31206</t>
+          <t>30904</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73368</t>
+          <t>73808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108157</t>
+          <t>108009</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>459283</t>
+          <t>458865</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>488893</t>
+          <t>487943</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136576</t>
+          <t>136878</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153646</t>
+          <t>154975</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602014</t>
+          <t>602162</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>636803</t>
+          <t>636363</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>179743</t>
+          <t>179080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>230559</t>
+          <t>232073</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75621</t>
+          <t>75947</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111944</t>
+          <t>112128</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>265418</t>
+          <t>267801</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>325594</t>
+          <t>331400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1007775</t>
+          <t>1006261</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1058591</t>
+          <t>1059254</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>602341</t>
+          <t>602157</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>638664</t>
+          <t>638338</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1627026</t>
+          <t>1621220</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1687202</t>
+          <t>1684819</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,29%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38433</t>
+          <t>37874</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64893</t>
+          <t>64066</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63475</t>
+          <t>64850</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99595</t>
+          <t>100626</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>110656</t>
+          <t>109479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>156324</t>
+          <t>152088</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>284812</t>
+          <t>285639</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>311272</t>
+          <t>311831</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>469157</t>
+          <t>468126</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>505277</t>
+          <t>503902</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>762133</t>
+          <t>766369</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>807801</t>
+          <t>808978</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,08%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20180</t>
+          <t>20107</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>247947</t>
+          <t>248072</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>305879</t>
+          <t>307026</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>259153</t>
+          <t>258408</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>319758</t>
+          <t>319322</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>277106</t>
+          <t>277179</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290690</t>
+          <t>291228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>941965</t>
+          <t>940818</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>999897</t>
+          <t>999772</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1225372</t>
+          <t>1225808</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1285977</t>
+          <t>1286722</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,28%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>417111</t>
+          <t>419404</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>493850</t>
+          <t>494639</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>496309</t>
+          <t>494686</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>575906</t>
+          <t>577790</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>933432</t>
+          <t>932643</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1046199</t>
+          <t>1048885</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2774575</t>
+          <t>2773786</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2851314</t>
+          <t>2849021</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2800321</t>
+          <t>2798437</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2879918</t>
+          <t>2881541</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5598453</t>
+          <t>5595767</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5711220</t>
+          <t>5712009</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51277</t>
+          <t>51858</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82999</t>
+          <t>83578</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25558</t>
+          <t>26783</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50685</t>
+          <t>50640</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83412</t>
+          <t>83903</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121951</t>
+          <t>124115</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>353197</t>
+          <t>352618</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>384919</t>
+          <t>384338</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263769</t>
+          <t>263814</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288896</t>
+          <t>287671</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>628699</t>
+          <t>626535</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>667238</t>
+          <t>666747</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,82%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64167</t>
+          <t>60007</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98965</t>
+          <t>97407</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21823</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44812</t>
+          <t>45102</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90860</t>
+          <t>90898</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133789</t>
+          <t>137130</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>319832</t>
+          <t>321390</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>354630</t>
+          <t>358790</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>292128</t>
+          <t>291838</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>315117</t>
+          <t>315146</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>621948</t>
+          <t>618607</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>664877</t>
+          <t>664839</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93124</t>
+          <t>93518</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133508</t>
+          <t>132755</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>21962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42895</t>
+          <t>44703</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121465</t>
+          <t>121109</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>169319</t>
+          <t>166298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>494877</t>
+          <t>495630</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535261</t>
+          <t>534867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>217234</t>
+          <t>215426</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>238677</t>
+          <t>238167</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>719196</t>
+          <t>722217</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>767050</t>
+          <t>767406</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,37%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>201305</t>
+          <t>201656</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>257694</t>
+          <t>255638</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75929</t>
+          <t>76396</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115640</t>
+          <t>113068</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>287949</t>
+          <t>289275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>355920</t>
+          <t>353796</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>901315</t>
+          <t>903371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>957704</t>
+          <t>957353</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>651017</t>
+          <t>653589</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>690728</t>
+          <t>690261</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1569747</t>
+          <t>1571871</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1637718</t>
+          <t>1636392</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,98%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77341</t>
+          <t>76318</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111734</t>
+          <t>111443</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>128932</t>
+          <t>128338</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>173064</t>
+          <t>173647</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>218068</t>
+          <t>218458</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>272428</t>
+          <t>271827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>397835</t>
+          <t>398126</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>432228</t>
+          <t>433251</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>588458</t>
+          <t>587875</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>632590</t>
+          <t>633184</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>998663</t>
+          <t>999264</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1053023</t>
+          <t>1052633</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,81%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14292</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33996</t>
+          <t>33720</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275608</t>
+          <t>273008</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>337332</t>
+          <t>333552</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>292696</t>
+          <t>295358</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>356889</t>
+          <t>358785</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230934</t>
+          <t>231210</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250638</t>
+          <t>250756</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>772019</t>
+          <t>775799</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>833743</t>
+          <t>836343</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1017392</t>
+          <t>1015496</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1081585</t>
+          <t>1078923</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,51%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>560676</t>
+          <t>557927</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>646853</t>
+          <t>660902</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>600878</t>
+          <t>598292</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>696172</t>
+          <t>698706</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1182665</t>
+          <t>1185327</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1315438</t>
+          <t>1318145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2770033</t>
+          <t>2755984</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2856210</t>
+          <t>2858959</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2852882</t>
+          <t>2850348</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2948176</t>
+          <t>2950762</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5650502</t>
+          <t>5647795</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5783275</t>
+          <t>5780613</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,98%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51039</t>
+          <t>49866</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81710</t>
+          <t>81816</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33318</t>
+          <t>33559</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62272</t>
+          <t>60569</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91576</t>
+          <t>90867</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133082</t>
+          <t>132897</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>347382</t>
+          <t>347276</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>378053</t>
+          <t>379226</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>284783</t>
+          <t>286486</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313737</t>
+          <t>313496</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>643065</t>
+          <t>643250</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>684571</t>
+          <t>685280</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37952</t>
+          <t>38627</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64659</t>
+          <t>66182</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22955</t>
+          <t>23532</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45608</t>
+          <t>44347</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67424</t>
+          <t>68138</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102478</t>
+          <t>103467</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>312568</t>
+          <t>311045</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>339275</t>
+          <t>338600</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326665</t>
+          <t>327926</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349318</t>
+          <t>348741</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>647022</t>
+          <t>646033</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>682076</t>
+          <t>681362</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72285</t>
+          <t>74142</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108172</t>
+          <t>107463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19564</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39665</t>
+          <t>42253</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100339</t>
+          <t>99167</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139288</t>
+          <t>139176</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>413742</t>
+          <t>414451</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>449629</t>
+          <t>447772</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126458</t>
+          <t>123870</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>146559</t>
+          <t>146646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>548748</t>
+          <t>548860</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>587697</t>
+          <t>588869</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,59%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171870</t>
+          <t>171796</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>222817</t>
+          <t>221682</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84632</t>
+          <t>85150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124049</t>
+          <t>127060</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>267315</t>
+          <t>268525</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>330557</t>
+          <t>328995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>926821</t>
+          <t>927956</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>977768</t>
+          <t>977842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>701827</t>
+          <t>698816</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>741244</t>
+          <t>740726</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1644957</t>
+          <t>1646519</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1708199</t>
+          <t>1706989</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,41%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96911</t>
+          <t>97138</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135082</t>
+          <t>133687</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>103083</t>
+          <t>104702</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145380</t>
+          <t>144877</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>210379</t>
+          <t>209178</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>265194</t>
+          <t>265864</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>485624</t>
+          <t>487019</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>523795</t>
+          <t>523568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>592864</t>
+          <t>593367</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>635161</t>
+          <t>633542</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1093756</t>
+          <t>1093086</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1148571</t>
+          <t>1149772</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,61%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10398</t>
+          <t>9730</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27109</t>
+          <t>28418</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>243726</t>
+          <t>244205</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>304513</t>
+          <t>303664</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>260345</t>
+          <t>259790</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>322355</t>
+          <t>323907</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>260036</t>
+          <t>258727</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>276747</t>
+          <t>277415</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>777512</t>
+          <t>778361</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>838299</t>
+          <t>837820</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1046815</t>
+          <t>1045263</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1108825</t>
+          <t>1109380</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,03%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>495989</t>
+          <t>486302</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>577202</t>
+          <t>578068</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>559667</t>
+          <t>564274</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>655704</t>
+          <t>660604</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1077897</t>
+          <t>1082621</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1205914</t>
+          <t>1210355</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2808520</t>
+          <t>2807654</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2889733</t>
+          <t>2899420</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2875892</t>
+          <t>2870992</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2971929</t>
+          <t>2967322</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5711404</t>
+          <t>5706963</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5839421</t>
+          <t>5834697</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,35%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>191081</t>
+          <t>207134</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>170456</t>
+          <t>184411</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>215108</t>
+          <t>228628</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>162997</t>
+          <t>178300</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>146712</t>
+          <t>159190</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>181851</t>
+          <t>196816</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>354078</t>
+          <t>385435</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>328519</t>
+          <t>357915</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>385345</t>
+          <t>414574</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>39,9%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>314131</t>
+          <t>343484</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>290104</t>
+          <t>321990</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>334756</t>
+          <t>366207</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>284470</t>
+          <t>310111</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265616</t>
+          <t>291595</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300755</t>
+          <t>329221</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>598601</t>
+          <t>653594</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>567334</t>
+          <t>624455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>624160</t>
+          <t>681114</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,55%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>167865</t>
+          <t>180264</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148493</t>
+          <t>157391</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>190195</t>
+          <t>201747</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>116029</t>
+          <t>128253</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>102128</t>
+          <t>112213</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>131812</t>
+          <t>145208</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,27 +9046,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>283895</t>
+          <t>308517</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>258785</t>
+          <t>281995</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>310145</t>
+          <t>336740</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>284348</t>
+          <t>302948</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>262018</t>
+          <t>281465</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>303720</t>
+          <t>325821</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>266551</t>
+          <t>294890</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>250768</t>
+          <t>277935</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>280452</t>
+          <t>310930</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,22 +9159,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>550898</t>
+          <t>597838</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>524648</t>
+          <t>569615</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>576008</t>
+          <t>624360</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,89%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>136014</t>
+          <t>149008</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56111</t>
+          <t>129479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>224603</t>
+          <t>168669</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>65771</t>
+          <t>72858</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56135</t>
+          <t>62322</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75731</t>
+          <t>83152</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>201785</t>
+          <t>221866</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90331</t>
+          <t>198635</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>292084</t>
+          <t>243356</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>532250</t>
+          <t>322604</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>443661</t>
+          <t>302943</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>612153</t>
+          <t>342133</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>101140</t>
+          <t>114639</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91180</t>
+          <t>104345</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110776</t>
+          <t>125175</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>633390</t>
+          <t>437243</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>543091</t>
+          <t>415753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>744844</t>
+          <t>460474</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>345683</t>
+          <t>378731</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>314864</t>
+          <t>347591</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>378911</t>
+          <t>410261</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>443947</t>
+          <t>260541</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>293659</t>
+          <t>237294</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>654919</t>
+          <t>282121</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>789629</t>
+          <t>639271</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>637342</t>
+          <t>598967</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1154243</t>
+          <t>677706</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>34,0%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>689136</t>
+          <t>753112</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>655908</t>
+          <t>721582</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>719955</t>
+          <t>784252</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>534147</t>
+          <t>600670</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>323175</t>
+          <t>579090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>684435</t>
+          <t>623917</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1223283</t>
+          <t>1353783</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>858669</t>
+          <t>1315348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1375570</t>
+          <t>1394087</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>69,95%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>128895</t>
+          <t>140443</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109552</t>
+          <t>121131</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147834</t>
+          <t>158636</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>266515</t>
+          <t>293509</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>199457</t>
+          <t>271866</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>305586</t>
+          <t>316159</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>395410</t>
+          <t>433952</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>307689</t>
+          <t>401221</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>433357</t>
+          <t>466687</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>346151</t>
+          <t>427521</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>327212</t>
+          <t>409328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>365494</t>
+          <t>446833</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>572481</t>
+          <t>536618</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>533410</t>
+          <t>513968</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>639539</t>
+          <t>558261</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>918631</t>
+          <t>964139</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>880684</t>
+          <t>931404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1006352</t>
+          <t>996870</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>71,3%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>11835</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26946</t>
+          <t>23067</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>350434</t>
+          <t>379148</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>327708</t>
+          <t>354254</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>374763</t>
+          <t>408414</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>363415</t>
+          <t>390983</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>329664</t>
+          <t>357047</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>391740</t>
+          <t>422008</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,02%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>227526</t>
+          <t>225393</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213561</t>
+          <t>214161</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233995</t>
+          <t>230841</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>410937</t>
+          <t>465133</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>386608</t>
+          <t>435867</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>433663</t>
+          <t>490027</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>638463</t>
+          <t>690526</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>610138</t>
+          <t>659501</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>672214</t>
+          <t>724462</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,99%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>982519</t>
+          <t>1067414</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>781514</t>
+          <t>1013109</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1071862</t>
+          <t>1121160</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1405692</t>
+          <t>1312609</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1252539</t>
+          <t>1265670</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1879841</t>
+          <t>1362545</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2388211</t>
+          <t>2380024</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2149000</t>
+          <t>2308095</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2831238</t>
+          <t>2452717</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2393541</t>
+          <t>2375062</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2304198</t>
+          <t>2321316</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2594546</t>
+          <t>2429367</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2169726</t>
+          <t>2322061</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1695577</t>
+          <t>2272125</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2322879</t>
+          <t>2369000</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4563268</t>
+          <t>4697122</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4120241</t>
+          <t>4624429</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4802479</t>
+          <t>4769051</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>67,39%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6951479</t>
+          <t>7077146</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6951479</t>
+          <t>7077146</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6951479</t>
+          <t>7077146</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
